--- a/Result/profitability/6925.xlsx
+++ b/Result/profitability/6925.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM18"/>
+  <dimension ref="A1:AM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2716,6 +2716,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6925</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>52</v>
+      </c>
+      <c r="D19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" t="n">
+        <v>40</v>
+      </c>
+      <c r="F19" t="n">
+        <v>76.89</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>28.23%</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>17</v>
+      </c>
+      <c r="K19" t="n">
+        <v>14</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.72375</v>
+      </c>
+      <c r="N19" t="n">
+        <v>79.68625</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.2999999999999999</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.7692307692307689</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.439999999999998</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.01908548707753477</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-4.310000000000002</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.05307881773399015</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK19" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
